--- a/public/exports-from-60-with-coowners/29189374.xlsx
+++ b/public/exports-from-60-with-coowners/29189374.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461926</t>
+          <t xml:space="preserve">311461967</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189374.xlsx
+++ b/public/exports-from-60-with-coowners/29189374.xlsx
@@ -8989,12 +8989,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461967</t>
+          <t xml:space="preserve">311461926</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
